--- a/vendor_application_form_templates/029_fulfillment_partner_accreditation_application--vendor_application_form_templates.xlsx
+++ b/vendor_application_form_templates/029_fulfillment_partner_accreditation_application--vendor_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1198,8 +1198,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'logistics'}</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Logistics'}</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'3pl'}</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': '3PL'}</t>
+          <t>3PL</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'warehousing'}</t>
+          <t>warehousing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Warehousing'}</t>
+          <t>Warehousing</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'packaging'}</t>
+          <t>packaging</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Packaging'}</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'less_than_5_years'}</t>
+          <t>less_than_5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Less than 5 years'}</t>
+          <t>Less than 5 years</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'north_america'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'North America'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'new_application'}</t>
+          <t>new_application</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'New Application'}</t>
+          <t>New Application</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'existing_application'}</t>
+          <t>existing_application</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Existing Application'}</t>
+          <t>Existing Application</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'re-application'}</t>
+          <t>re-application</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Re-Application'}</t>
+          <t>Re-Application</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'new_application'}</t>
+          <t>new_application</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'New Application'}</t>
+          <t>New Application</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'existing_application'}</t>
+          <t>existing_application</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Existing Application'}</t>
+          <t>Existing Application</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'re-application'}</t>
+          <t>re-application</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Re-Application'}</t>
+          <t>Re-Application</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'new_application'}</t>
+          <t>new_application</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'New Application'}</t>
+          <t>New Application</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'existing_application'}</t>
+          <t>existing_application</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'Existing Application'}</t>
+          <t>Existing Application</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'re-application'}</t>
+          <t>re-application</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'Re-Application'}</t>
+          <t>Re-Application</t>
         </is>
       </c>
     </row>
